--- a/leave_request_forms/013_pharmacy_staff_leave_month_selection--leave_request_forms.xlsx
+++ b/leave_request_forms/013_pharmacy_staff_leave_month_selection--leave_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'leave_month'}</t>
+          <t>leave_month</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'leave_month'}</t>
+          <t>leave month</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'leave_type'}</t>
+          <t>leave_type</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'leave_type'}</t>
+          <t>leave type</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'vacation'}</t>
+          <t>vacation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Vacation'}</t>
+          <t>Vacation</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'sick'}</t>
+          <t>sick</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Sick'}</t>
+          <t>Sick</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
